--- a/artfynd/A 34065-2025 artfynd.xlsx
+++ b/artfynd/A 34065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273276</v>
+        <v>113273313</v>
       </c>
       <c r="B2" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>2080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576295</v>
+        <v>576280</v>
       </c>
       <c r="R2" t="n">
-        <v>6651986</v>
+        <v>6652002</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>smågrynig</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113273275</v>
+        <v>113273274</v>
       </c>
       <c r="B3" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576233</v>
+        <v>576036</v>
       </c>
       <c r="R3" t="n">
-        <v>6651968</v>
+        <v>6651889</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273274</v>
+        <v>113273275</v>
       </c>
       <c r="B4" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576036</v>
+        <v>576233</v>
       </c>
       <c r="R4" t="n">
-        <v>6651889</v>
+        <v>6651968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273344</v>
+        <v>113273276</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576204</v>
+        <v>576295</v>
       </c>
       <c r="R5" t="n">
-        <v>6651959</v>
+        <v>6651986</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1077,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113273333</v>
+        <v>113273314</v>
       </c>
       <c r="B6" t="n">
-        <v>90723</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576296</v>
+        <v>576211</v>
       </c>
       <c r="R6" t="n">
-        <v>6651986</v>
+        <v>6651969</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1183,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1218,6 +1198,213 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113273347</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Myggsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576003</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6651899</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113273333</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Myggsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576296</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6651986</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>

--- a/artfynd/A 34065-2025 artfynd.xlsx
+++ b/artfynd/A 34065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273274</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273275</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273276</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273314</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273347</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,8 +1444,22 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273333</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>